--- a/Report/Test_cases_WisdomITNews.xlsx
+++ b/Report/Test_cases_WisdomITNews.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8400"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="363">
   <si>
     <t>TCID</t>
   </si>
@@ -1131,275 +1131,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Bài báo mới
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Gemini trả về nhãn (AiLabel)
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-ClassifyCategoryAsync()
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Tra bảng CategoryMappings
-      │
- ┌────</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>┴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">────┐
- │         │
-Có         Không
- │         │
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">         </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Trả CategoryId   AI tự suy luận
- │         │
- └────</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>┬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">────┘
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Bài được lưu
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Admin kiểm tra
-      │
-Sai?
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-CorrectArticleCategory()
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Cập nhật CategoryMappings
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Lần nhập bài sau
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-ClassifyCategoryAsync() tra được quy tắc mới
-      │
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>▼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Phân loại đúng ngay từ đầu</t>
-    </r>
-  </si>
-  <si>
     <t>1. Sửa danh mục một bài ngoài.
 2. Nhập lại bài tương tự.
 3. Kiểm tra danh mục đúng theo quy tắc.</t>
@@ -1573,7 +1304,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1610,13 +1341,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1768,7 +1492,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1802,12 +1526,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1910,12 +1628,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2134,67 +1846,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2209,22 +1924,25 @@
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2233,10 +1951,10 @@
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2245,10 +1963,10 @@
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2257,10 +1975,10 @@
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2269,17 +1987,11 @@
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2310,12 +2022,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4410,7 +4116,7 @@
       <c r="D74" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F74" s="6" t="s">
@@ -4437,7 +4143,7 @@
       <c r="D75" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="10" t="s">
         <v>200</v>
       </c>
       <c r="F75" s="6" t="s">
@@ -5001,7 +4707,7 @@
       <c r="D99" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="10" t="s">
         <v>263</v>
       </c>
       <c r="F99" s="6" t="s">
@@ -5482,28 +5188,28 @@
       <c r="C119" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="E119" s="13" t="s">
+      <c r="E119" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I119" s="7" t="s">
         <v>316</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:9">
       <c r="A120" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -5520,25 +5226,25 @@
       </c>
       <c r="B121" s="7"/>
       <c r="C121" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D121" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="E121" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I121" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="122" ht="96" customHeight="1" spans="1:9">
@@ -5547,25 +5253,25 @@
       </c>
       <c r="B122" s="7"/>
       <c r="C122" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D122" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="E122" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I122" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="123" ht="111" customHeight="1" spans="1:9">
@@ -5574,30 +5280,30 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D123" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="E123" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I123" s="7" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:9">
       <c r="A124" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5614,25 +5320,25 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D125" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="E125" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I125" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I125" s="7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="126" ht="96" customHeight="1" spans="1:9">
@@ -5641,25 +5347,25 @@
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="E126" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I126" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I126" s="7" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="127" ht="96" customHeight="1" spans="1:9">
@@ -5668,25 +5374,25 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D127" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="E127" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I127" s="7" t="s">
         <v>336</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I127" s="7" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="128" ht="171" customHeight="1" spans="1:9">
@@ -5695,25 +5401,25 @@
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D128" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="E128" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="E128" s="8" t="s">
+      <c r="F128" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I128" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I128" s="7" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="129" ht="141" customHeight="1" spans="1:9">
@@ -5722,30 +5428,30 @@
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D129" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="D129" s="7" t="s">
+      <c r="E129" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I129" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H129" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I129" s="7" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:9">
       <c r="A130" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -5762,25 +5468,25 @@
       </c>
       <c r="B131" s="7"/>
       <c r="C131" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D131" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="E131" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I131" s="7" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="132" ht="96" customHeight="1" spans="1:9">
@@ -5789,25 +5495,25 @@
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="E132" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I132" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I132" s="7" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="133" ht="126" customHeight="1" spans="1:9">
@@ -5816,25 +5522,25 @@
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="E133" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I133" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I133" s="7" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="134" ht="96" customHeight="1" spans="1:9">
@@ -5843,25 +5549,25 @@
       </c>
       <c r="B134" s="7"/>
       <c r="C134" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D134" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="E134" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I134" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I134" s="7" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="135" ht="126" customHeight="1" spans="1:9">
@@ -5870,25 +5576,25 @@
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D135" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="D135" s="7" t="s">
+      <c r="E135" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I135" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I135" s="7" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="136" ht="126" customHeight="1" spans="1:9">
@@ -5897,25 +5603,25 @@
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D136" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="E136" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I136" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I136" s="7" t="s">
-        <v>363</v>
       </c>
     </row>
   </sheetData>
